--- a/data/trans_orig/IMC_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2007</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2007 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164254</t>
+          <t>167635</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>214122</t>
+          <t>218475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>296928</t>
+          <t>296874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>358691</t>
+          <t>356407</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>474791</t>
+          <t>477868</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>557835</t>
+          <t>557640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>475615</t>
+          <t>474810</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>539543</t>
+          <t>537256</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>522518</t>
+          <t>525797</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>596207</t>
+          <t>596066</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1020806</t>
+          <t>1026426</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1117961</t>
+          <t>1115491</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>277542</t>
+          <t>278904</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>336715</t>
+          <t>337064</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>353456</t>
+          <t>347860</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>419591</t>
+          <t>419970</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>645418</t>
+          <t>647942</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>736132</t>
+          <t>736335</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18012</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15061</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34047</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132344</t>
+          <t>131435</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181397</t>
+          <t>176629</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117731</t>
+          <t>112923</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>162723</t>
+          <t>159659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>266462</t>
+          <t>264126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>326256</t>
+          <t>330715</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>736935</t>
+          <t>736335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>816036</t>
+          <t>816590</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>385110</t>
+          <t>386176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>454261</t>
+          <t>450659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1137857</t>
+          <t>1140366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1248621</t>
+          <t>1253241</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>701992</t>
+          <t>704794</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>784513</t>
+          <t>785257</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>924306</t>
+          <t>924352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1001622</t>
+          <t>1003847</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1652379</t>
+          <t>1651575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1768269</t>
+          <t>1765568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>17192</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40242</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70332</t>
+          <t>69199</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47812</t>
+          <t>48672</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>79420</t>
+          <t>78401</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>37208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68974</t>
+          <t>68458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44100</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65466</t>
+          <t>66167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101436</t>
+          <t>104284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>219738</t>
+          <t>222155</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>268733</t>
+          <t>270271</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>80465</t>
+          <t>81526</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>117419</t>
+          <t>118765</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>313086</t>
+          <t>313667</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>378447</t>
+          <t>376269</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>226910</t>
+          <t>225692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>276120</t>
+          <t>276178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>299242</t>
+          <t>299858</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>341338</t>
+          <t>340976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>538923</t>
+          <t>539108</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>605838</t>
+          <t>604287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,27%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31195</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12366</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30899</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>357630</t>
+          <t>359914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>435047</t>
+          <t>437874</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>459750</t>
+          <t>459824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>536007</t>
+          <t>544169</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>839139</t>
+          <t>840877</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>952012</t>
+          <t>954599</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1474611</t>
+          <t>1472216</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1585898</t>
+          <t>1579551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1023027</t>
+          <t>1023184</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1132522</t>
+          <t>1128316</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2525296</t>
+          <t>2530920</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2682956</t>
+          <t>2679083</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1245329</t>
+          <t>1245487</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1353862</t>
+          <t>1359462</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1612605</t>
+          <t>1610607</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1730446</t>
+          <t>1728089</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2897465</t>
+          <t>2894168</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3057593</t>
+          <t>3051497</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>29049</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69619</t>
+          <t>69404</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>108081</t>
+          <t>106736</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87505</t>
+          <t>87751</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129649</t>
+          <t>125838</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2012</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2012 (tasa de respuesta: 96,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205183</t>
+          <t>209544</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>261931</t>
+          <t>263652</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>394623</t>
+          <t>392202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>466573</t>
+          <t>462577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>620453</t>
+          <t>613875</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>708273</t>
+          <t>701291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421277</t>
+          <t>423339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490865</t>
+          <t>486551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>462508</t>
+          <t>464673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>534767</t>
+          <t>537816</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>907903</t>
+          <t>911810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1003486</t>
+          <t>1007116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,24%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>219121</t>
+          <t>218307</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>276680</t>
+          <t>272712</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>275095</t>
+          <t>270993</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>336778</t>
+          <t>334861</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>513150</t>
+          <t>502462</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>588697</t>
+          <t>590765</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>14994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>240442</t>
+          <t>241715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>302390</t>
+          <t>303881</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>231006</t>
+          <t>228881</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>293069</t>
+          <t>290141</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>490038</t>
+          <t>489037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>578108</t>
+          <t>577347</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>910037</t>
+          <t>914622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1002615</t>
+          <t>1002278</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>487293</t>
+          <t>491134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>569980</t>
+          <t>564244</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1421836</t>
+          <t>1423782</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1546729</t>
+          <t>1545975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645612</t>
+          <t>648032</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>733635</t>
+          <t>731071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>817006</t>
+          <t>816914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>906549</t>
+          <t>900644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1486108</t>
+          <t>1489755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1613387</t>
+          <t>1612443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32509</t>
+          <t>33163</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49335</t>
+          <t>50278</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81271</t>
+          <t>81782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69294</t>
+          <t>69207</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106259</t>
+          <t>103914</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37842</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66594</t>
+          <t>65642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>39394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60283</t>
+          <t>60102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97893</t>
+          <t>96883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>202095</t>
+          <t>201405</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>250029</t>
+          <t>251081</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85220</t>
+          <t>89300</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124100</t>
+          <t>129903</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>299658</t>
+          <t>301624</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>363838</t>
+          <t>363035</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,18%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>172682</t>
+          <t>171431</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217342</t>
+          <t>218638</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>286675</t>
+          <t>282081</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>326061</t>
+          <t>327223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>467118</t>
+          <t>468642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>534112</t>
+          <t>531702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24905</t>
+          <t>24111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24937</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>511736</t>
+          <t>511331</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>600668</t>
+          <t>598734</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>670044</t>
+          <t>664828</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>767991</t>
+          <t>767024</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1203340</t>
+          <t>1203029</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1333559</t>
+          <t>1332521</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1580720</t>
+          <t>1582986</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1698583</t>
+          <t>1703343</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1072814</t>
+          <t>1074697</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1194070</t>
+          <t>1185228</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2688038</t>
+          <t>2686380</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2850651</t>
+          <t>2860507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1064200</t>
+          <t>1074437</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1183655</t>
+          <t>1184476</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1409505</t>
+          <t>1409423</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1536582</t>
+          <t>1532693</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2522950</t>
+          <t>2519346</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2684731</t>
+          <t>2681772</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20603</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42861</t>
+          <t>45034</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68306</t>
+          <t>67017</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104217</t>
+          <t>102108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95931</t>
+          <t>96247</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137259</t>
+          <t>136886</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2016</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2016 (tasa de respuesta: 95,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146304</t>
+          <t>145420</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>190934</t>
+          <t>191145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>267193</t>
+          <t>267616</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>325581</t>
+          <t>329938</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>428811</t>
+          <t>426709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>503756</t>
+          <t>499957</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>331009</t>
+          <t>329576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383844</t>
+          <t>382299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319032</t>
+          <t>319587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>382072</t>
+          <t>380443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>668987</t>
+          <t>669757</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743965</t>
+          <t>750003</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,03%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160455</t>
+          <t>160649</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206008</t>
+          <t>206813</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>201576</t>
+          <t>202600</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>253846</t>
+          <t>254963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>373832</t>
+          <t>377383</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>450231</t>
+          <t>447513</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21479</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>291986</t>
+          <t>292632</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>359236</t>
+          <t>357348</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>244535</t>
+          <t>247305</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>307194</t>
+          <t>309997</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>554103</t>
+          <t>559065</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>649505</t>
+          <t>652223</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>807951</t>
+          <t>804477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>893875</t>
+          <t>891172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>591629</t>
+          <t>590909</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>675469</t>
+          <t>679225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1418945</t>
+          <t>1413116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1540185</t>
+          <t>1540062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>772114</t>
+          <t>770137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>859499</t>
+          <t>859994</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>909560</t>
+          <t>906469</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1000328</t>
+          <t>995025</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1714284</t>
+          <t>1702096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1834351</t>
+          <t>1831354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34859</t>
+          <t>34578</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48837</t>
+          <t>47377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78534</t>
+          <t>78259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69515</t>
+          <t>67861</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106103</t>
+          <t>104077</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46393</t>
+          <t>47550</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78163</t>
+          <t>79725</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>38046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64554</t>
+          <t>65395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91373</t>
+          <t>92362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134402</t>
+          <t>134079</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>195275</t>
+          <t>194137</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>242062</t>
+          <t>243344</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>117011</t>
+          <t>117073</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>157345</t>
+          <t>157422</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>326854</t>
+          <t>325774</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>388398</t>
+          <t>389415</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>227191</t>
+          <t>224115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>273282</t>
+          <t>275225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>303137</t>
+          <t>304423</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>347901</t>
+          <t>347791</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>542580</t>
+          <t>540772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>608387</t>
+          <t>607351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19432</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>514912</t>
+          <t>511930</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>604112</t>
+          <t>599169</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>578240</t>
+          <t>578512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>668782</t>
+          <t>676768</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1117484</t>
+          <t>1113929</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1242036</t>
+          <t>1244545</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1366371</t>
+          <t>1371100</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1477343</t>
+          <t>1496142</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1056655</t>
+          <t>1063450</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1171254</t>
+          <t>1170610</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2469905</t>
+          <t>2465697</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2621916</t>
+          <t>2630185</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1189850</t>
+          <t>1192409</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1297328</t>
+          <t>1300841</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1452294</t>
+          <t>1445199</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1569741</t>
+          <t>1565758</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2670467</t>
+          <t>2672335</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2832593</t>
+          <t>2831828</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41234</t>
+          <t>43174</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65324</t>
+          <t>65269</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>100514</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90267</t>
+          <t>93460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132222</t>
+          <t>136161</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2023</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2023 (tasa de respuesta: 96,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108203</t>
+          <t>106937</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142806</t>
+          <t>143507</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,82 +8269,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>29,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>195501</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>179594</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>214255</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>28,37%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>26,07%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>31,1%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>320005</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>294957</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>343367</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>29,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>195501</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>177229</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>214694</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>28,37%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>25,72%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>320005</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>295662</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>346475</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>27,13%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>25,06%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>226506</t>
+          <t>225514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265911</t>
+          <t>267120</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296203</t>
+          <t>296555</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>335535</t>
+          <t>337337</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>537254</t>
+          <t>534689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>592705</t>
+          <t>593475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,31%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98823</t>
+          <t>96758</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132823</t>
+          <t>130562</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153639</t>
+          <t>152801</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>189013</t>
+          <t>189734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>259322</t>
+          <t>260699</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310710</t>
+          <t>312541</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17781</t>
+          <t>18153</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>366403</t>
+          <t>365886</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1103082</t>
+          <t>1087565</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>305099</t>
+          <t>307201</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1015141</t>
+          <t>1019547</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>705598</t>
+          <t>705554</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1705337</t>
+          <t>1763727</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>614745</t>
+          <t>621590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1015922</t>
+          <t>1022001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>499528</t>
+          <t>510701</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>822623</t>
+          <t>818910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1276051</t>
+          <t>1263150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1765080</t>
+          <t>1760436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506937</t>
+          <t>536522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>875556</t>
+          <t>871161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>653276</t>
+          <t>646894</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1057170</t>
+          <t>1050973</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1322766</t>
+          <t>1308411</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1867065</t>
+          <t>1864110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15097</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61929</t>
+          <t>58386</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38288</t>
+          <t>39979</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79190</t>
+          <t>80231</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64177</t>
+          <t>63312</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>122398</t>
+          <t>122672</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64314</t>
+          <t>64932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102186</t>
+          <t>100339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54884</t>
+          <t>54394</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82917</t>
+          <t>81792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>125867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172512</t>
+          <t>170663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>251068</t>
+          <t>251791</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>306669</t>
+          <t>306993</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>147431</t>
+          <t>146042</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>186280</t>
+          <t>185794</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>410756</t>
+          <t>412209</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>479752</t>
+          <t>478353</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>245304</t>
+          <t>247396</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>304133</t>
+          <t>304009</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>375053</t>
+          <t>373156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>417433</t>
+          <t>417950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>634331</t>
+          <t>635175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>704799</t>
+          <t>706414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>20994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21468</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>570574</t>
+          <t>570231</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1388522</t>
+          <t>1380124</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>572697</t>
+          <t>570687</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1334447</t>
+          <t>1316273</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1180493</t>
+          <t>1162141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2299235</t>
+          <t>2192646</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1064839</t>
+          <t>1101870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1544932</t>
+          <t>1551344</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>973376</t>
+          <t>964132</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1306229</t>
+          <t>1296894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2242174</t>
+          <t>2290621</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2776895</t>
+          <t>2803191</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>883815</t>
+          <t>888335</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1264485</t>
+          <t>1258976</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1170600</t>
+          <t>1158289</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1609566</t>
+          <t>1613238</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2268310</t>
+          <t>2302123</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2835976</t>
+          <t>2841149</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68198</t>
+          <t>68308</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57900</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98290</t>
+          <t>98523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86250</t>
+          <t>89002</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>144405</t>
+          <t>149016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>167635</t>
+          <t>163759</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>218475</t>
+          <t>214689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>296874</t>
+          <t>296861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>356407</t>
+          <t>360518</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>477868</t>
+          <t>474665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>557640</t>
+          <t>552325</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>474810</t>
+          <t>477961</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>537256</t>
+          <t>540953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>525797</t>
+          <t>524099</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>596066</t>
+          <t>597080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1026426</t>
+          <t>1016317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1115491</t>
+          <t>1110657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>278904</t>
+          <t>278305</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>337064</t>
+          <t>336915</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>347860</t>
+          <t>352916</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>419970</t>
+          <t>421546</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>647942</t>
+          <t>649067</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>736335</t>
+          <t>735624</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21394</t>
+          <t>21432</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33683</t>
+          <t>34066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131435</t>
+          <t>133253</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>176629</t>
+          <t>182095</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>112923</t>
+          <t>117109</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>159659</t>
+          <t>160676</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>264126</t>
+          <t>264004</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>330715</t>
+          <t>333047</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>736335</t>
+          <t>733566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>816590</t>
+          <t>815371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>386176</t>
+          <t>386540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>450659</t>
+          <t>453876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1140366</t>
+          <t>1138664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1253241</t>
+          <t>1249274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>704794</t>
+          <t>703550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>785257</t>
+          <t>787251</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>924352</t>
+          <t>925708</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1003847</t>
+          <t>1001151</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1651575</t>
+          <t>1650595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1765568</t>
+          <t>1761691</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17192</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40157</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69199</t>
+          <t>68762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48672</t>
+          <t>46879</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78401</t>
+          <t>80076</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37208</t>
+          <t>37625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68458</t>
+          <t>65420</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46794</t>
+          <t>45626</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66167</t>
+          <t>66208</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104284</t>
+          <t>103704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>222155</t>
+          <t>222372</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>270271</t>
+          <t>269564</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81526</t>
+          <t>81521</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118765</t>
+          <t>119149</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>313667</t>
+          <t>313187</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>376269</t>
+          <t>374011</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>225692</t>
+          <t>226385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>276178</t>
+          <t>274216</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>299858</t>
+          <t>298915</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340976</t>
+          <t>342164</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>539108</t>
+          <t>540281</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>604287</t>
+          <t>604782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12649</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13261</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30699</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>359914</t>
+          <t>359204</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>437874</t>
+          <t>432962</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>459824</t>
+          <t>460185</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>544169</t>
+          <t>542817</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>840877</t>
+          <t>838073</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>954599</t>
+          <t>949602</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1472216</t>
+          <t>1472692</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1579551</t>
+          <t>1587361</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1023184</t>
+          <t>1023298</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1128316</t>
+          <t>1128583</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2530920</t>
+          <t>2526228</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2679083</t>
+          <t>2690112</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1245487</t>
+          <t>1246114</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1359462</t>
+          <t>1358303</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1610607</t>
+          <t>1617218</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1728089</t>
+          <t>1727964</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2894168</t>
+          <t>2885137</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3051497</t>
+          <t>3048522</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29049</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69404</t>
+          <t>70946</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106736</t>
+          <t>107350</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87751</t>
+          <t>87153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125838</t>
+          <t>126746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209544</t>
+          <t>206801</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>263652</t>
+          <t>261670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>392202</t>
+          <t>395706</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>462577</t>
+          <t>462859</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>613875</t>
+          <t>617063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>701291</t>
+          <t>701269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423339</t>
+          <t>422543</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486551</t>
+          <t>489267</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>464673</t>
+          <t>466392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>537816</t>
+          <t>538743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>911810</t>
+          <t>910053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1007116</t>
+          <t>1005624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>218307</t>
+          <t>216952</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>272712</t>
+          <t>274410</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>270993</t>
+          <t>272591</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>334861</t>
+          <t>334170</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>502462</t>
+          <t>506208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>590765</t>
+          <t>587283</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14994</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20632</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>241715</t>
+          <t>238174</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>303881</t>
+          <t>300785</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>228881</t>
+          <t>230222</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>290141</t>
+          <t>293230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>489037</t>
+          <t>488074</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>577347</t>
+          <t>578282</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>914622</t>
+          <t>910975</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1002278</t>
+          <t>1001778</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>491134</t>
+          <t>486802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>564244</t>
+          <t>563976</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1423782</t>
+          <t>1423806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1545975</t>
+          <t>1541821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>648032</t>
+          <t>649792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>731071</t>
+          <t>735153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>816914</t>
+          <t>821932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>900644</t>
+          <t>902484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1489755</t>
+          <t>1489824</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1612443</t>
+          <t>1605612</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33163</t>
+          <t>32812</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50278</t>
+          <t>49398</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81782</t>
+          <t>82026</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69207</t>
+          <t>67257</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103914</t>
+          <t>105906</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>35078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65642</t>
+          <t>66383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>18631</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39394</t>
+          <t>42220</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60102</t>
+          <t>62161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96883</t>
+          <t>98396</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>201405</t>
+          <t>203157</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>251081</t>
+          <t>248452</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>89300</t>
+          <t>87549</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>129903</t>
+          <t>124519</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>301624</t>
+          <t>300941</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>363035</t>
+          <t>363241</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>171431</t>
+          <t>174211</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>218638</t>
+          <t>219776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>282081</t>
+          <t>284885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>327223</t>
+          <t>327215</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>468642</t>
+          <t>469402</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>531702</t>
+          <t>533508</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>24616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25692</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>511331</t>
+          <t>510590</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>598734</t>
+          <t>600276</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>664828</t>
+          <t>669388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>767024</t>
+          <t>762926</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1203029</t>
+          <t>1202307</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1332521</t>
+          <t>1336757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1582986</t>
+          <t>1579612</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1703343</t>
+          <t>1697683</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1074697</t>
+          <t>1079160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1185228</t>
+          <t>1194556</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2686380</t>
+          <t>2691945</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2860507</t>
+          <t>2860712</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1074437</t>
+          <t>1074871</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1184476</t>
+          <t>1192950</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1409423</t>
+          <t>1406447</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1532693</t>
+          <t>1530910</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2519346</t>
+          <t>2522249</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2681772</t>
+          <t>2689390</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45034</t>
+          <t>43976</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67017</t>
+          <t>67619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102108</t>
+          <t>102249</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96247</t>
+          <t>94569</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136886</t>
+          <t>136316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145420</t>
+          <t>146764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>191145</t>
+          <t>189839</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>267616</t>
+          <t>268395</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>329938</t>
+          <t>330158</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>426709</t>
+          <t>426250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>499957</t>
+          <t>504547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>329576</t>
+          <t>332995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382299</t>
+          <t>385074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319587</t>
+          <t>321864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>380443</t>
+          <t>379488</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>669757</t>
+          <t>669071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750003</t>
+          <t>748364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206813</t>
+          <t>208713</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>202600</t>
+          <t>199704</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>254963</t>
+          <t>253978</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>377383</t>
+          <t>375179</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>447513</t>
+          <t>447364</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>18683</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21943</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>292632</t>
+          <t>292715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>357348</t>
+          <t>360148</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247305</t>
+          <t>245375</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>309997</t>
+          <t>307420</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>559065</t>
+          <t>557194</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>652223</t>
+          <t>651677</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>804477</t>
+          <t>803915</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>891172</t>
+          <t>895090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>590909</t>
+          <t>587406</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>679225</t>
+          <t>669118</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1413116</t>
+          <t>1420184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1540062</t>
+          <t>1546235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>770137</t>
+          <t>769162</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>859994</t>
+          <t>857561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>906469</t>
+          <t>910560</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>995025</t>
+          <t>995415</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1702096</t>
+          <t>1700206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1831354</t>
+          <t>1830183</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>14897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34578</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47377</t>
+          <t>48134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78259</t>
+          <t>78609</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67861</t>
+          <t>70260</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>104077</t>
+          <t>105430</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47550</t>
+          <t>46812</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79725</t>
+          <t>78702</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38046</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65395</t>
+          <t>65608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92362</t>
+          <t>91951</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134079</t>
+          <t>134422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>194137</t>
+          <t>196825</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>243344</t>
+          <t>240321</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>117073</t>
+          <t>116256</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>157422</t>
+          <t>159331</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>325774</t>
+          <t>327150</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>389415</t>
+          <t>387046</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>224115</t>
+          <t>229101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>275225</t>
+          <t>272025</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>304423</t>
+          <t>303198</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>347791</t>
+          <t>351310</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>540772</t>
+          <t>545034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>607351</t>
+          <t>609148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,65%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22302</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>511930</t>
+          <t>514177</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>599169</t>
+          <t>606384</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>578512</t>
+          <t>579970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>676768</t>
+          <t>673527</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1113929</t>
+          <t>1115894</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1244545</t>
+          <t>1241004</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1371100</t>
+          <t>1370687</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1496142</t>
+          <t>1482987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1063450</t>
+          <t>1063279</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1170610</t>
+          <t>1175217</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2465697</t>
+          <t>2457517</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2630185</t>
+          <t>2615147</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1192409</t>
+          <t>1191928</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1300841</t>
+          <t>1301638</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1445199</t>
+          <t>1447184</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1565758</t>
+          <t>1565787</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2672335</t>
+          <t>2685877</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2831828</t>
+          <t>2849826</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43174</t>
+          <t>42276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>65424</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100514</t>
+          <t>99686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93460</t>
+          <t>91682</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136161</t>
+          <t>133409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -8249,22 +8249,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>124503</t>
+          <t>136057</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106937</t>
+          <t>118716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>143507</t>
+          <t>157789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>195501</t>
+          <t>215713</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>179594</t>
+          <t>198226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>214255</t>
+          <t>235437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>320005</t>
+          <t>351770</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>294957</t>
+          <t>325071</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>343367</t>
+          <t>380299</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>246812</t>
+          <t>269384</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225514</t>
+          <t>244724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267120</t>
+          <t>289409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,17 +8397,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>316796</t>
+          <t>345369</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296555</t>
+          <t>323495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337337</t>
+          <t>364955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>563609</t>
+          <t>614753</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>534689</t>
+          <t>583800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>593475</t>
+          <t>647078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>114009</t>
+          <t>133339</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96758</t>
+          <t>113839</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130562</t>
+          <t>151476</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>171026</t>
+          <t>184119</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>152801</t>
+          <t>166711</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>189734</t>
+          <t>203934</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>285035</t>
+          <t>317458</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>260699</t>
+          <t>292138</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>312541</t>
+          <t>346390</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,27 +8623,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18153</t>
+          <t>18570</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>490628</t>
+          <t>544488</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490628</t>
+          <t>544488</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490628</t>
+          <t>544488</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>689005</t>
+          <t>751152</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>689005</t>
+          <t>751152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>689005</t>
+          <t>751152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1179634</t>
+          <t>1295640</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1179634</t>
+          <t>1295640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1179634</t>
+          <t>1295640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>582194</t>
+          <t>360756</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>365886</t>
+          <t>324785</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1087565</t>
+          <t>401717</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>493382</t>
+          <t>323082</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>307201</t>
+          <t>295149</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1019547</t>
+          <t>352071</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1075576</t>
+          <t>683839</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>705554</t>
+          <t>638229</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1763727</t>
+          <t>730804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>889085</t>
+          <t>972078</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>621590</t>
+          <t>915662</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1022001</t>
+          <t>1023596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>688278</t>
+          <t>701698</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>510701</t>
+          <t>665594</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>818910</t>
+          <t>746869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1577363</t>
+          <t>1673776</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1263150</t>
+          <t>1603139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1760436</t>
+          <t>1738918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>762505</t>
+          <t>838254</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>536522</t>
+          <t>786234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>871161</t>
+          <t>890621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>923222</t>
+          <t>1035307</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646894</t>
+          <t>989656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1050973</t>
+          <t>1077250</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1685728</t>
+          <t>1873561</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1308411</t>
+          <t>1807898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1864110</t>
+          <t>1944087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30608</t>
+          <t>26405</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58386</t>
+          <t>47832</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58609</t>
+          <t>61759</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39979</t>
+          <t>45803</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80231</t>
+          <t>82174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>89216</t>
+          <t>88164</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63312</t>
+          <t>66582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>122672</t>
+          <t>115801</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2264392</t>
+          <t>2197493</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2264392</t>
+          <t>2197493</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2264392</t>
+          <t>2197493</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2163490</t>
+          <t>2121845</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2163490</t>
+          <t>2121845</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2163490</t>
+          <t>2121845</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4427883</t>
+          <t>4319339</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4427883</t>
+          <t>4319339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4427883</t>
+          <t>4319339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>81547</t>
+          <t>88297</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64932</t>
+          <t>71791</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100339</t>
+          <t>109064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>66843</t>
+          <t>76478</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54394</t>
+          <t>63751</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81792</t>
+          <t>93038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>148390</t>
+          <t>164775</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125867</t>
+          <t>142500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170663</t>
+          <t>189017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>278928</t>
+          <t>303893</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>251791</t>
+          <t>273574</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>306993</t>
+          <t>331540</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166115</t>
+          <t>189335</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>146042</t>
+          <t>170051</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>185794</t>
+          <t>211878</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>445043</t>
+          <t>493228</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>412209</t>
+          <t>457618</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>478353</t>
+          <t>529557</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>274317</t>
+          <t>305533</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>247396</t>
+          <t>276551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>304009</t>
+          <t>336304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>395482</t>
+          <t>433010</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>373156</t>
+          <t>408018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>417950</t>
+          <t>453866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>669800</t>
+          <t>738543</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>635175</t>
+          <t>699870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>706414</t>
+          <t>774621</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,82%</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -9736,12 +9736,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>15249</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>16368</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20967</t>
+          <t>26454</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>635866</t>
+          <t>698842</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>635866</t>
+          <t>698842</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>635866</t>
+          <t>698842</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>640952</t>
+          <t>714072</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>640952</t>
+          <t>714072</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>640952</t>
+          <t>714072</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1276818</t>
+          <t>1412913</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1276818</t>
+          <t>1412913</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1276818</t>
+          <t>1412913</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>788244</t>
+          <t>585110</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>570231</t>
+          <t>542205</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1380124</t>
+          <t>631582</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>755726</t>
+          <t>615273</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>570687</t>
+          <t>574887</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1316273</t>
+          <t>654036</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1543970</t>
+          <t>1200384</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1162141</t>
+          <t>1140039</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2192646</t>
+          <t>1260723</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1414826</t>
+          <t>1545355</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1101870</t>
+          <t>1478272</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1551344</t>
+          <t>1607431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1171189</t>
+          <t>1236402</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>964132</t>
+          <t>1187231</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1296894</t>
+          <t>1290021</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2586015</t>
+          <t>2781757</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2290621</t>
+          <t>2700278</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2803191</t>
+          <t>2863534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1150832</t>
+          <t>1277125</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>888335</t>
+          <t>1213568</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1258976</t>
+          <t>1346462</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1489730</t>
+          <t>1652436</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1158289</t>
+          <t>1599964</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1613238</t>
+          <t>1706488</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2640562</t>
+          <t>2929561</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2302123</t>
+          <t>2848724</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2841149</t>
+          <t>3015805</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>36984</t>
+          <t>33233</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68308</t>
+          <t>57325</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>76803</t>
+          <t>82958</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>65669</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98523</t>
+          <t>103436</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,17 +10365,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>113787</t>
+          <t>116191</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89002</t>
+          <t>93525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>149016</t>
+          <t>145270</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3390887</t>
+          <t>3440823</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3390887</t>
+          <t>3440823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3390887</t>
+          <t>3440823</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3493448</t>
+          <t>3587069</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3493448</t>
+          <t>3587069</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3493448</t>
+          <t>3587069</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6884334</t>
+          <t>7027893</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6884334</t>
+          <t>7027893</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6884334</t>
+          <t>7027893</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
